--- a/frontend/sample/kelvara-systems-grant-analysis.xlsx
+++ b/frontend/sample/kelvara-systems-grant-analysis.xlsx
@@ -1292,7 +1292,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Get help with these applications</t>
+          <t>Want help winning a grant?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Built by Thomas Murray, a consultant who helps climate and deeptech startups win grant funding. This shortlist is the same landscape scan I run at the start of a client engagement — if you want help turning any of these into a submitted application, get in touch.</t>
+          <t>I'm Thomas Murray. I help climate and deep tech startups win grant funding and achieve profitability. This tool is a productised version of an opportunity assessment I've done for several startups. If you want help turning a grant opportunity into a complete application, contact me.</t>
         </is>
       </c>
     </row>

--- a/frontend/sample/kelvara-systems-grant-analysis.xlsx
+++ b/frontend/sample/kelvara-systems-grant-analysis.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.63" customWidth="1" min="1" max="1"/>
@@ -1062,8 +1062,2564 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem Long Duration Electricity Storage (LDES) Cap and Floor Regime — Window 2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem's LDES cap and floor regime is designed to de-risk long-duration energy storage projects in the UK grid — directly relevant to Kelvara's grid-scale thermal battery providing 8+ hour storage. Window 1 advanced 16 projects in June 2026; Window 2 is expected. This is the primary UK policy instrument for LDES commercialisation.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Concessional | Revenue support mechanism — project-specific; no fixed grant amount</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ofgem.gov.uk/decision/long-duration-electricity-storage-cap-and-floor-application-window-1</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Completion of the 5 MWh commercial pilot and identification of a UK grid-connected deployment site would make Kelvara eligible to apply for Window 2 as a project entity seeking revenue support for a grid-scale LDES deployment.</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>known future window</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Window 2 application process not yet confirmed open, and the revenue support mechanism requires a grid-connected project at a scale and maturity likely beyond Kelvara's current 500 kWh demonstration — the application route is unclear for a seed-stage company.</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Unclear Application Route</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ARENA / AMGC Industrial Electrification Fund</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>The fund explicitly targets electrification of industrial processes reliant on fossil fuels for SME manufacturers — a direct thematic match for Kelvara's thermal battery enabling process heat electrification. Opens July 2026, assessed on a continuous basis until December 2027.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Grant | $10M total fund; individual grant amounts unknown</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://arena.gov.au/funding/</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Australian Renewable Energy Agency (ARENA) / Advanced Manufacturing Growth Centre (AMGC)</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Establishing an Australian entity or partnering with an Australian industrial manufacturer as co-applicant would make this fund accessible — worth pursuing if Kelvara's Australia expansion progresses in 2026-2027.</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>known future window</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Kelvara lists Australia as only an exploratory geography with no confirmed operational presence or Australian-registered entity — the fund requires Australian SME manufacturers, creating a geography and entity eligibility barrier.</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Direct Startup Application</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem Strategic Innovation Fund (SIF) — Discovery C6</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SIF funds energy network innovation including grid flexibility and storage; Kelvara's thermal battery provides long-duration grid flexibility by absorbing surplus renewables, aligning with SIF's network innovation objectives.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2484/overview/770c0946-2e24-4566-bab1-2bf1c1dd2b38</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Ofgem / Innovate UK</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Identify a licensed or regulated organisation (network operator, NHS trust, housing association, or local authority) willing to act as lead applicant, with the startup named as the technology partner.</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but not deep-researched. It likely requires a licensed or regulated entity (e.g. network operator, NHS trust, housing association, or local authority) as lead applicant. The startup may be able to participate as a named technology partner. Verify current eligibility and identify a suitable lead organisation.</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK Knowledge Transfer Partnership (KTP) — 2026-2027 Round 3 (anticipated)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>KTP supports UK SMEs to embed academic expertise into innovation projects; Kelvara as a university spinout could use KTP to accelerate R&amp;D on PCM thermal storage with a UK university partner.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/innovate-uk/guidance-for-applicants/guidance-for-specific-funds/knowledge-transfer-partnership-guidance/dates-and-deadlines-for-ktp-applicants/</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK / UKRI</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MBIE Strategic Science Investment Fund (SSIF) — Advanced Energy Technology Platform</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>SSIF Advanced Energy Technology Platform funds NZ-based advanced energy technology R&amp;D; Kelvara's aluminium-alloy PCM thermal battery is a novel advanced energy technology with NZ HQ.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.mbie.govt.nz/science-and-technology/science-and-innovation/funding-information-and-opportunities/investment-funds/strategic-science-investment-fund</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Business, Innovation and Employment (MBIE), New Zealand</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Callaghan Innovation — R&amp;D Project Grant (New Zealand)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Callaghan Innovation funds NZ-based SME R&amp;D projects; Kelvara's seed-stage thermal battery development with NZ HQ is a strong fit for project grant support.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.callaghaninnovation.govt.nz/</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Callaghan Innovation, New Zealand</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EIT InnoEnergy — Call for Proposals (Energy Storage / Industrial Decarbonisation)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EIT InnoEnergy explicitly funds energy storage, renewable energy, and energy efficiency innovations for industrial applications — core to Kelvara's thermal battery product.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Blended | unknown</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>https://innoenergy.com/</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>EIT InnoEnergy</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>EU Member States and associated countries</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>UK Flexibility Innovation Programme — DESNZ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Programme supports innovative solutions for large-scale electricity system flexibility — directly relevant to Kelvara's thermal battery absorbing surplus renewables and providing grid flexibility.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/flexibility-innovation</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Department for Energy Security and Net Zero (DESNZ)</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Government — Industrial Energy Efficiency and Decarbonisation Fund</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Government fund supports industrial sites investing in energy efficiency and decarbonisation — directly aligned with Kelvara's thermal battery for industrial process heat replacement.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.scot/collections/scottish-industrial-energy-transformation-fund-sietf/</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Scottish Government / Scottish Enterprise</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Scotland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>UKRI Net Zero Industrial Decarbonisation Challenge — specific competition (2026-2027)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>UKRI's industrial decarbonisation challenge funds target exactly the sectors Kelvara serves (food, chemicals, paper) and the technology approach (electrification of process heat).</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/councils/innovate-uk/</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>UKRI / Innovate UK</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK — Next Wave: Breakthrough Wave 1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Programme supports UK SMEs developing breakthrough technologies at the intersection of deep tech and UK Industrial Strategy priorities, which includes net zero and energy — relevant to Kelvara's deep tech thermal battery.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2517/overview/6ff2066d-4639-44e6-bb4f-ce7099222739</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK / UKRI</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EU Innovation Fund — Large-Scale Projects Call (next round, 2026-2027)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Innovation Fund large-scale calls fund highly innovative low-carbon technologies including energy storage and industrial decarbonisation — strong alignment with Kelvara's grid-scale thermal battery.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/programmes/innovation-fund_en</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>European Commission (Innovation Fund / CINEA)</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>EU Member States and EEA/associated countries</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK — Sustainable Innovation Fund / Net Zero Transition Fund (2026-2027 round)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK net zero transition competitions fund UK SMEs developing clean energy and decarbonisation technologies — directly relevant to Kelvara's thermal battery for industrial emissions reduction.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/search</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK / UKRI</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Horizon Europe — Processes4Planet Partnership (industrial process decarbonisation)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Processes4Planet targets optimisation of energy and materials use in industrial processes including recycling and upcycling — partial alignment with Kelvara's circular economy use of recycled aluminium and industrial process heat.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/calls-for-proposals?callIdentifier=HORIZON-CID-2027-01</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>European Commission / Horizon Europe</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>EU Member States and associated countries</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>UK Research Fund for Coal and Steel (RFCS) — complementary call via Horizon Europe</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>RFCS funds decarbonisation of energy-intensive industries including steel and chemicals — sectors where Kelvara's thermal battery could displace fossil-fuel process heat, though primary focus is coal/steel sector.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/programmes/rfcs</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>European Commission</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>EU Member States</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK — Industrial Decarbonisation Challenge (IDC) follow-on competitions</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>IDC aims to establish net-zero carbon industrial clusters in the UK; Kelvara's thermal battery enabling industrial process heat decarbonisation is a core enabling technology for this mission.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ukri.org/what-we-do/browse-our-areas-of-investment-and-support/industrial-decarbonisation/</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK / UKRI</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand Green Investment Finance (NZGIF) — Concessional Finance for Industrial Decarbonisation</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>NZGIF provides concessional finance to accelerate NZ's transition to a low-emissions economy; Kelvara's industrial thermal battery for NZ industrial decarbonisation is within its mandate.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Concessional | unknown</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>https://nzgif.co.nz/</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand Green Investment Finance (NZGIF)</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Breakthrough Energy Fellows / Breakthrough Energy Ventures — Catalyst Programme</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Breakthrough Energy Catalyst funds first-of-kind clean energy projects including long-duration storage and industrial decarbonisation — directly aligned with Kelvara's thermal battery technology.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>https://breakthroughenergy.org/our-work/catalyst/</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Breakthrough Energy</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Horizon Europe — Battery Partnership (Batteries2030+ / BATT4EU) — Energy Storage Innovation</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Battery partnership calls include energy storage innovation beyond lithium-ion; Kelvara's aluminium-alloy PCM thermal battery as a novel grid-scale storage medium has partial fit, though primary focus is electrochemical batteries.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Grant | unknown</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/programmes/horizon</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>European Commission / Horizon Europe</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Review the programme's eligibility criteria and application process directly to determine whether the startup can apply.</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>EU Member States and associated countries</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>timing unknown</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>This programme was identified during discovery but was not selected for deep research. It showed partial thematic fit — verify eligibility and application process directly.</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Direct applicant</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>Recurring</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EIC Accelerator Open — Deep Tech for Climate Adaptation Challenge (2026)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>The named 'Deep Tech for Climate Adaptation' challenge is a direct match for Kelvara's climate hardware for industrial decarbonisation — a high-risk, deep-tech thermal battery at TRL 6 seeking commercialisation funding is precisely the EIC Accelerator's intended beneficiary.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Blended | Up to €2.5M grant + up to €15M equity (grant-only track available)</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>https://eic.ec.europa.eu/eic-funding-opportunities/eic-accelerator/eic-accelerator-challenges-2026/deep-tech-climate-adaptation_en</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>European Innovation Council (EIC)</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>The next application round opening — monitor the programme page and prepare the application in advance.</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>EU Member States and associated countries (UK associated)</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>open now</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Well-established recurring programme with no application window currently open. The EIC Accelerator is a well-known, institutionalised recurring EU fund with confirmed 2026 Challenges rounds; the current_link points directly to the specific Deep Tech for Climate Adaptation challenge page, and no contradicting evidence suggests it has been cancelled.</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Direct Startup Application</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK — Industrial Energy Transformation Fund (IETF) Phase 4</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>IETF's primary purpose is funding capital investment in industrial energy efficiency and heat decarbonisation — Kelvara's thermal battery for replacing fossil-fuel process heat is a textbook IETF project.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Grant | Up to £14.5M per project (feasibility: up to £80K; capital: up to £14.5M)</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/collections/industrial-energy-transformation-fund</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Innovate UK / Department for Energy Security and Net Zero (DESNZ)</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>The next application round opening — monitor the programme page and prepare the application in advance.</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>open now</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Well-established recurring programme with no application window currently open. The IETF is a well-established recurring UK government fund with multiple prior phases; search results returned no relevant evidence, but the programme's documented history of open rounds and the official GOV.UK collection page support a 'likely' status.</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Direct Startup Application</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B5">
+  <conditionalFormatting sqref="B2:B26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1073,7 +3629,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D5">
+  <conditionalFormatting sqref="D2:D26">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1083,7 +3639,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F5">
+  <conditionalFormatting sqref="F2:F26">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1093,7 +3649,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H5">
+  <conditionalFormatting sqref="H2:H26">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1103,7 +3659,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J5">
+  <conditionalFormatting sqref="J2:J26">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1113,7 +3669,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N5">
+  <conditionalFormatting sqref="N2:N26">
     <cfRule type="expression" priority="6" dxfId="0">
       <formula>AND(ISNUMBER(N2),TRUNC(N2)&lt;TODAY())</formula>
     </cfRule>
@@ -1123,6 +3679,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/frontend/sample/kelvara-systems-grant-analysis.xlsx
+++ b/frontend/sample/kelvara-systems-grant-analysis.xlsx
@@ -1088,20 +1088,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -1210,20 +1206,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -1332,20 +1324,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1454,20 +1442,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1576,20 +1560,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -1698,20 +1678,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1820,20 +1796,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1942,20 +1914,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -2064,20 +2032,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -2186,20 +2150,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -2308,20 +2268,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -2430,20 +2386,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -2552,20 +2504,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -2674,20 +2622,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -2796,20 +2740,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -2918,20 +2858,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -3040,20 +2976,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -3162,20 +3094,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -3284,20 +3212,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -3386,10 +3310,9 @@
           <t>EIC Accelerator Open — Deep Tech for Climate Adaptation Challenge (2026)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="B25" s="2">
+        <f>(2*D25)+F25+H25</f>
+        <v/>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -3404,20 +3327,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -3504,10 +3423,9 @@
           <t>Innovate UK — Industrial Energy Transformation Fund (IETF) Phase 4</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="B26" s="2">
+        <f>(2*D26)+F26+H26</f>
+        <v/>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -3522,20 +3440,16 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
